--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137053454</v>
+        <v>137073393</v>
       </c>
       <c r="B6" t="n">
-        <v>8463</v>
+        <v>57954</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,37 +1144,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Getgärdet, Getgärdet, Ög</t>
+          <t>Bärtorpet, Bärtorpet, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541764</v>
+        <v>541827</v>
       </c>
       <c r="R6" t="n">
-        <v>6491253</v>
+        <v>6491269</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,19 +1206,14 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:11</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stjärtpenna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,16 +1239,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137053454</t>
+          <t>https://artportalen.se/Sighting/137073393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137055034</v>
+        <v>137053454</v>
       </c>
       <c r="B7" t="n">
-        <v>111340</v>
+        <v>8463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220240</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541782</v>
+        <v>541764</v>
       </c>
       <c r="R7" t="n">
-        <v>6491194</v>
+        <v>6491253</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,16 +1351,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137055034</t>
+          <t>https://artportalen.se/Sighting/137053454</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137055010</v>
+        <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>98226</v>
+        <v>111340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,16 +1368,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>220240</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541821</v>
+        <v>541782</v>
       </c>
       <c r="R8" t="n">
-        <v>6491257</v>
+        <v>6491194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,6 +1462,118 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137055034</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137055010</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98226</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getgärdet, Getgärdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>541821</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6491257</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137055010</t>
         </is>
@@ -1476,6 +1588,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96665</v>
+        <v>96671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96671</v>
+        <v>96675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96677</v>
+        <v>96679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137055459</v>
       </c>
       <c r="B2" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96679</v>
+        <v>96692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137073393</v>
       </c>
       <c r="B6" t="n">
-        <v>57954</v>
+        <v>57967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137055459</v>
       </c>
       <c r="B2" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137073393</v>
       </c>
       <c r="B6" t="n">
-        <v>57967</v>
+        <v>57969</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137053454</v>
       </c>
       <c r="B7" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -1162,11 +1162,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bärtorpet, Bärtorpet, Ög</t>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137055459</v>
       </c>
       <c r="B2" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137073393</v>
       </c>
       <c r="B6" t="n">
-        <v>57969</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137053454</v>
       </c>
       <c r="B7" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137055459</v>
       </c>
       <c r="B2" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137073393</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137055459</v>
       </c>
       <c r="B2" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137073393</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38702-2026 artfynd.xlsx
+++ b/artfynd/A 38702-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137055459</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137052993</v>
       </c>
       <c r="B3" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137052871</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137055097</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137073393</v>
       </c>
       <c r="B6" t="n">
-        <v>57981</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137055034</v>
       </c>
       <c r="B8" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137055010</v>
       </c>
       <c r="B9" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
